--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512411_ELIMINATORIAS18FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512411_ELIMINATORIAS18FINAL_PROCESSED.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. SOLER CIRUJEDA</t>
+          <t>K. GREELEY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8636</v>
+        <v>5.1103</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2713</v>
+        <v>3.8178</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5922</v>
+        <v>1.2925</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6254</v>
+        <v>2.534</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3372</v>
+        <v>1.7978</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2881</v>
+        <v>0.7362</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3802</v>
+        <v>3.9289</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5084</v>
+        <v>2.0532</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8717</v>
+        <v>1.8757</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2452</v>
+        <v>-1.3949</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1712</v>
+        <v>-0.2553</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4164</v>
+        <v>-1.1395</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8194</v>
+        <v>2.8343</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0485</v>
+        <v>-0.2025</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2291</v>
+        <v>3.0368</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5286999999999999</v>
+        <v>-0.8531</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1073</v>
+        <v>-0.5038</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4215</v>
+        <v>-0.3493</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5288</v>
+        <v>0.5951</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8324</v>
+        <v>0.5951</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6965</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. GREELEY</t>
+          <t>J. SOLER CIRUJEDA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1446</v>
+        <v>4.6566</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8672</v>
+        <v>2.3298</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2774</v>
+        <v>2.3268</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5086</v>
+        <v>3.63</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7786</v>
+        <v>0.3361</v>
       </c>
       <c r="I3" t="n">
-        <v>0.73</v>
+        <v>3.2939</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8488</v>
+        <v>3.4322</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0021</v>
+        <v>1.5402</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8467</v>
+        <v>1.892</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3402</v>
+        <v>0.1978</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2235</v>
+        <v>-1.2041</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1167</v>
+        <v>1.4019</v>
       </c>
       <c r="P3" t="n">
-        <v>2.8679</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2048</v>
+        <v>-2.0245</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0727</v>
+        <v>1.2147</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.8222</v>
+        <v>0.302</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3671</v>
+        <v>0.076</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4551</v>
+        <v>0.226</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5903</v>
+        <v>1.5344</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5903</v>
+        <v>0.846</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5384</v>
+        <v>3.5545</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7877</v>
+        <v>1.7482</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7508</v>
+        <v>1.8063</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1817</v>
+        <v>1.2119</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2712</v>
+        <v>1.2842</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0895</v>
+        <v>-0.0723</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6149</v>
+        <v>1.6722</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2157</v>
+        <v>1.2439</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3992</v>
+        <v>0.4283</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4332</v>
+        <v>-0.4602</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0555</v>
+        <v>0.0403</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4887</v>
+        <v>-0.5006</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0215</v>
+        <v>0.0346</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1728</v>
+        <v>0.076</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1513</v>
+        <v>-0.0414</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9254</v>
+        <v>2.0186</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0519</v>
+        <v>0.9023</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8735000000000001</v>
+        <v>1.1163</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5243</v>
+        <v>0.5421</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.8924</v>
+        <v>-1.8786</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4167</v>
+        <v>2.4207</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1117</v>
+        <v>0.167</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.1673</v>
+        <v>-1.1287</v>
       </c>
       <c r="L5" t="n">
-        <v>1.279</v>
+        <v>1.2957</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4126</v>
+        <v>0.3752</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7251</v>
+        <v>-0.7499</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1377</v>
+        <v>1.1251</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4798</v>
+        <v>-0.3941</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.786</v>
+        <v>-0.0174</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6938</v>
+        <v>-0.3766</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7262</v>
+        <v>0.7528</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BARBER TERRADES</t>
+          <t>J. SANTANA LUCHORO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0655</v>
+        <v>0.0067</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0655</v>
+        <v>-0.5592</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.5659</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1.384</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.3356</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1.0484</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.7838</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.2037</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.3998</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.8682</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.4684</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.227</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.6196</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0655</v>
+        <v>-0.5191</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0655</v>
+        <v>-0.1161</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.403</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.2509</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SANTANA LUCHORO</t>
+          <t>J. MOLINA MARTINEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1952</v>
+        <v>-0.6872</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6119</v>
+        <v>-2.526</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4167</v>
+        <v>1.8388</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3808</v>
+        <v>-1.3819</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3263</v>
+        <v>-0.1184</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0545</v>
+        <v>-1.2635</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7307</v>
+        <v>-0.7418</v>
       </c>
       <c r="K7" t="n">
-        <v>1.163</v>
+        <v>0.0388</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5677</v>
+        <v>-0.7806</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3499</v>
+        <v>-0.6401</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8367</v>
+        <v>-0.1572</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4868</v>
+        <v>-0.4829</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6145</v>
+        <v>0.4049</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2533</v>
+        <v>-2.0245</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6388</v>
+        <v>2.4294</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7193000000000001</v>
+        <v>0.2898</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0892</v>
+        <v>-0.0106</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6301</v>
+        <v>0.3004</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2421</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2509</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MOLINA MARTINEZ</t>
+          <t>C. OSAIKHWUWUOMWAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.659</v>
+        <v>-0.9107</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0008</v>
+        <v>-1.7465</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3418</v>
+        <v>0.8357</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3914</v>
+        <v>0.8494</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1143</v>
+        <v>-0.0784</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2771</v>
+        <v>0.9277</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.786</v>
+        <v>0.4944</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0253</v>
+        <v>0.4149</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8113</v>
+        <v>0.0795</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6054</v>
+        <v>0.355</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1396</v>
+        <v>-0.4932</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4658</v>
+        <v>0.8482</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4097</v>
+        <v>-1.4172</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4582</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3227</v>
+        <v>-0.092</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4084</v>
+        <v>-0.2163</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7311</v>
+        <v>0.1243</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2509</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2421</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. OSAIKHWUWUOMWAN</t>
+          <t>L. FERRANDO ORTELLS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7327</v>
+        <v>-1.0288</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9526</v>
+        <v>-2.3557</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2199</v>
+        <v>1.3268</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8737</v>
+        <v>-1.3061</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0643</v>
+        <v>-1.1854</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9379999999999999</v>
+        <v>-0.1207</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4888</v>
+        <v>0.0498</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4098</v>
+        <v>-1.2459</v>
       </c>
       <c r="L9" t="n">
-        <v>0.079</v>
+        <v>1.2957</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3849</v>
+        <v>-1.3559</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4741</v>
+        <v>0.0605</v>
       </c>
       <c r="O9" t="n">
-        <v>0.859</v>
+        <v>-1.4164</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.4339</v>
+        <v>0.4049</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0485</v>
+        <v>-2.227</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6145</v>
+        <v>2.6319</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0696</v>
+        <v>-0.8159</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.393</v>
+        <v>-0.1785</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4626</v>
+        <v>-0.6375</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2421</v>
+        <v>0.6883</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2421</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. PEREZ RAMIREZ</t>
+          <t>M. MONTILLA DIAZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0378</v>
+        <v>-1.8156</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7829</v>
+        <v>-2.8019</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.255</v>
+        <v>0.9863</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.3678</v>
+        <v>-2.4338</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5101</v>
+        <v>-2.8667</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.8577</v>
+        <v>0.433</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.7675</v>
+        <v>-2.6893</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6772</v>
+        <v>-2.6893</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0903</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6002999999999999</v>
+        <v>0.2556</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1671</v>
+        <v>-0.1774</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7674</v>
+        <v>0.433</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4097</v>
+        <v>1.0123</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2048</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6145</v>
+        <v>1.0123</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7397</v>
+        <v>-0.3941</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0089</v>
+        <v>-0.1125</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2692</v>
+        <v>-0.2815</v>
       </c>
       <c r="V10" t="n">
-        <v>1.1806</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1806</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. BITJAA KODY</t>
+          <t>G. PEREZ RAMIREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4098</v>
+        <v>-1.8182</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7377</v>
+        <v>-1.4772</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3279</v>
+        <v>-0.341</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.2323</v>
+        <v>-3.3674</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6805</v>
+        <v>-0.5138</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5519</v>
+        <v>-2.8537</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.0595</v>
+        <v>-2.7486</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9031</v>
+        <v>-0.6723</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1564</v>
+        <v>-2.0763</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1728</v>
+        <v>-0.6188</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2226</v>
+        <v>0.1586</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3954</v>
+        <v>-0.7774</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6388</v>
+        <v>0.4049</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.2291</v>
+        <v>-0.2025</v>
       </c>
       <c r="R11" t="n">
-        <v>2.8679</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9714</v>
+        <v>-0.0459</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5509</v>
+        <v>0.2836</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5795</v>
+        <v>-0.3296</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2124</v>
+        <v>1.1902</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1902</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. FERRANDO ORTELLS</t>
+          <t>J. BITJAA KODY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4665</v>
+        <v>-2.5944</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7051</v>
+        <v>-3.8403</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2386</v>
+        <v>1.2459</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2901</v>
+        <v>-4.2234</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1737</v>
+        <v>-1.6614</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1164</v>
+        <v>-2.562</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0221</v>
+        <v>-3.006</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2569</v>
+        <v>-1.8603</v>
       </c>
       <c r="L12" t="n">
-        <v>1.279</v>
+        <v>-1.1457</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3122</v>
+        <v>-1.2175</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0833</v>
+        <v>0.1989</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3954</v>
+        <v>-1.4164</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4097</v>
+        <v>1.6196</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2533</v>
+        <v>-1.2147</v>
       </c>
       <c r="R12" t="n">
-        <v>2.663</v>
+        <v>2.8343</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2826</v>
+        <v>-0.177</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4738</v>
+        <v>0.3804</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8088</v>
+        <v>-0.5574</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6965</v>
+        <v>0.1865</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6965</v>
+        <v>0.1865</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. MONTILLA DIAZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1423,151 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.0537</v>
+        <v>6.491800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.102</v>
+        <v>-6.508699999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0482</v>
+        <v>13.0003</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.4354</v>
+        <v>-2.561200000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.8764</v>
+        <v>-4.548999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.441</v>
+        <v>1.987700000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.709</v>
+        <v>2.342600000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.709</v>
+        <v>-1.1018</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.4444</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2736</v>
+        <v>-4.9036</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1674</v>
+        <v>-3.447</v>
       </c>
       <c r="O13" t="n">
-        <v>0.441</v>
+        <v>-1.4566</v>
       </c>
       <c r="P13" t="n">
-        <v>1.0242</v>
+        <v>7.085699999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-12.1472</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0242</v>
+        <v>19.233</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-2.6648</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.393</v>
+        <v>-0.3392</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2496</v>
+        <v>-2.3256</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>4.6319</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.635</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.9968</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. BURGOS CABALLERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PROINBENI UPB GANDIA</t>
+          <t>C.B. STARLABS MORÓN</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.851799999999996</v>
+        <v>2.9898</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.980399999999999</v>
+        <v>0.8254</v>
       </c>
       <c r="F14" t="n">
-        <v>13.832</v>
+        <v>2.1644</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.622500000000001</v>
+        <v>2.2019</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.5984</v>
+        <v>1.5231</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9757</v>
+        <v>0.6787</v>
       </c>
       <c r="J14" t="n">
-        <v>1.875200000000001</v>
+        <v>1.1821</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.3892</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>3.264299999999999</v>
+        <v>0.4518</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.4977</v>
+        <v>1.0198</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.2091</v>
+        <v>0.7929</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2885</v>
+        <v>0.2269</v>
       </c>
       <c r="P14" t="n">
-        <v>7.1698</v>
+        <v>0.2025</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.2908</v>
+        <v>-1.6196</v>
       </c>
       <c r="R14" t="n">
-        <v>19.4605</v>
+        <v>1.8221</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.3584</v>
+        <v>1.1806</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1361</v>
+        <v>1.012</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.2222</v>
+        <v>0.1686</v>
       </c>
       <c r="V14" t="n">
-        <v>4.663</v>
+        <v>-0.5951</v>
       </c>
       <c r="W14" t="n">
-        <v>3.571600000000001</v>
+        <v>0.2509</v>
       </c>
       <c r="X14" t="n">
-        <v>1.0915</v>
+        <v>-0.846</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BURGOS CABALLERO</t>
+          <t>J. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7369</v>
+        <v>2.1957</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6692</v>
+        <v>-1.4568</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0677</v>
+        <v>3.6525</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2114</v>
+        <v>3.5194</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5438</v>
+        <v>-1.185</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6676</v>
+        <v>4.7044</v>
       </c>
       <c r="J15" t="n">
-        <v>1.122</v>
+        <v>1.2064</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7083</v>
+        <v>-1.9577</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4137</v>
+        <v>3.1641</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0894</v>
+        <v>2.313</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8355</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2539</v>
+        <v>1.5403</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2048</v>
+        <v>-1.6196</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.6388</v>
+        <v>-3.2392</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8436</v>
+        <v>1.6196</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9109</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9439</v>
+        <v>0.576</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.033</v>
+        <v>-0.0292</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5903</v>
+        <v>-0.2509</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2421</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8324</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARIN ORTEGA</t>
+          <t>A. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6337</v>
+        <v>0.9935</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.8596</v>
+        <v>0.803</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4933</v>
+        <v>0.1905</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5266</v>
+        <v>0.5231</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1654</v>
+        <v>0.8882</v>
       </c>
       <c r="I16" t="n">
-        <v>4.692</v>
+        <v>-0.365</v>
       </c>
       <c r="J16" t="n">
-        <v>1.163</v>
+        <v>1.6613</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.9732</v>
+        <v>1.0253</v>
       </c>
       <c r="L16" t="n">
-        <v>3.1362</v>
+        <v>0.6361</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3635</v>
+        <v>-1.1382</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8078</v>
+        <v>-0.1371</v>
       </c>
       <c r="O16" t="n">
-        <v>1.5558</v>
+        <v>-1.0011</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.6388</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.2776</v>
+        <v>-1.6196</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6388</v>
+        <v>1.2147</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.012</v>
+        <v>0.1224</v>
       </c>
       <c r="T16" t="n">
-        <v>0.255</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.267</v>
+        <v>0.114</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2421</v>
+        <v>0.7528</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.7528</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8447</v>
+        <v>0.9588</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9941</v>
+        <v>1.0057</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1495</v>
+        <v>-0.0469</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1758</v>
+        <v>1.1716</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0278</v>
+        <v>0.0202</v>
       </c>
       <c r="I17" t="n">
-        <v>1.148</v>
+        <v>1.1514</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2645</v>
+        <v>1.2722</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2645</v>
+        <v>1.2722</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0887</v>
+        <v>-0.1006</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0278</v>
+        <v>0.0202</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1164</v>
+        <v>-0.1207</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1263</v>
+        <v>-0.0104</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0655</v>
+        <v>-0.064</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0608</v>
+        <v>0.0537</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,28 +1813,28 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2927</v>
+        <v>0.2963</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2927</v>
+        <v>0.2963</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2927</v>
+        <v>0.2963</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2927</v>
+        <v>0.2963</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2927</v>
+        <v>0.2963</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2927</v>
+        <v>0.2963</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MARIN ORTEGA</t>
+          <t>J. JIMENEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2083</v>
+        <v>-0.2677</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1499</v>
+        <v>-1.9648</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3582</v>
+        <v>1.6971</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.3596</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8617</v>
+        <v>1.4832</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3452</v>
+        <v>-1.1236</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6058</v>
+        <v>-0.1858</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9736</v>
+        <v>1.3032</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6322</v>
+        <v>-1.489</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0893</v>
+        <v>0.5454</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1119</v>
+        <v>0.1801</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9774</v>
+        <v>0.3654</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4097</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.6388</v>
+        <v>-2.4294</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2291</v>
+        <v>2.227</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6247</v>
+        <v>0.5144</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8431</v>
+        <v>0.3995</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2184</v>
+        <v>0.1149</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7262</v>
+        <v>-0.9393</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7262</v>
+        <v>0.2509</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Z. WILLIAMS</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3145</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7731</v>
+        <v>1.3693</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4586</v>
+        <v>-2.0996</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0673</v>
+        <v>0.4646</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2767</v>
+        <v>1.9164</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.344</v>
+        <v>-1.4518</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0449</v>
+        <v>2.7657</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8312</v>
+        <v>2.7657</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7863</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1122</v>
+        <v>-2.3011</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4455</v>
+        <v>-0.8493000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5577</v>
+        <v>-1.4518</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.0242</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2533</v>
+        <v>-1.0123</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2291</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>1.777</v>
+        <v>-0.2881</v>
       </c>
       <c r="T20" t="n">
-        <v>1.4353</v>
+        <v>-0.3842</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3417</v>
+        <v>0.096</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.5019</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>Z. WILLIAMS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.793</v>
+        <v>-1.1779</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3149</v>
+        <v>-1.6218</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1079</v>
+        <v>0.4439</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4545</v>
+        <v>-1.0524</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8957</v>
+        <v>1.2845</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4413</v>
+        <v>-2.3369</v>
       </c>
       <c r="J21" t="n">
-        <v>2.7321</v>
+        <v>0.1035</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7321</v>
+        <v>0.8679</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.7644</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2777</v>
+        <v>-1.1559</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8364</v>
+        <v>0.4166</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4413</v>
+        <v>-1.5725</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4097</v>
+        <v>-1.0123</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0242</v>
+        <v>-2.227</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6145</v>
+        <v>1.2147</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3537</v>
+        <v>0.8868</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.393</v>
+        <v>0.5016</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0393</v>
+        <v>0.3851</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.4841</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.4841</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. JIMENEZ GONZALEZ</t>
+          <t>G. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1326</v>
+        <v>-1.7747</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6129</v>
+        <v>-1.7297</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4803</v>
+        <v>-0.0451</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3568</v>
+        <v>-1.8239</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4966</v>
+        <v>-1.126</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1398</v>
+        <v>-0.6979</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2588</v>
+        <v>-1.2454</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2743</v>
+        <v>-0.6328</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.533</v>
+        <v>-0.6126</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6155</v>
+        <v>-0.5785</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2223</v>
+        <v>-0.4932</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3932</v>
+        <v>-0.0853</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2048</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4582</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2533</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.346</v>
+        <v>0.1302</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.138</v>
+        <v>-0.0469</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.208</v>
+        <v>0.177</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9385</v>
+        <v>-0.6883</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2421</v>
+        <v>-0.4374</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1806</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. FERNANDEZ DIAZ</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5498</v>
+        <v>-2.7952</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4554</v>
+        <v>-3.6478</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0944</v>
+        <v>0.8526</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8007</v>
+        <v>0.0125</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1124</v>
+        <v>0.0595</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6884</v>
+        <v>-0.047</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2559</v>
+        <v>0.4349</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6382</v>
+        <v>0.2759</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6177</v>
+        <v>0.159</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5448</v>
+        <v>-0.4224</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4741</v>
+        <v>-0.2164</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0706</v>
+        <v>-0.206</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6145</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.227</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6145</v>
+        <v>1.0123</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3329</v>
+        <v>0.221</v>
       </c>
       <c r="T23" t="n">
-        <v>0.255</v>
+        <v>-0.0417</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0779</v>
+        <v>0.2627</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6965</v>
+        <v>-1.8141</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.4544</v>
+        <v>-1.8141</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7223</v>
+        <v>-2.856</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.9894</v>
+        <v>-4.5868</v>
       </c>
       <c r="F24" t="n">
-        <v>2.2671</v>
+        <v>1.7308</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5909</v>
+        <v>-0.6166</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8364</v>
+        <v>-0.8493000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2455</v>
+        <v>0.2327</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5984</v>
+        <v>-0.5705</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.3097</v>
+        <v>-1.2861</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7113</v>
+        <v>0.7156</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0075</v>
+        <v>-0.0461</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4733</v>
+        <v>0.4367</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4658</v>
+        <v>-0.4829</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.5067</v>
+        <v>-4.4539</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9414</v>
+        <v>0.7973</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1156</v>
+        <v>0.4376</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8257</v>
+        <v>0.3597</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>L. PAREJO CAMACHO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.7646</v>
+        <v>-2.9914</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.6331</v>
+        <v>-2.2922</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8685</v>
+        <v>-0.6992</v>
       </c>
       <c r="G25" t="n">
-        <v>0.035</v>
+        <v>-2.495</v>
       </c>
       <c r="H25" t="n">
-        <v>0.064</v>
+        <v>0.238</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.029</v>
+        <v>-2.733</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4175</v>
+        <v>-2.017</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2595</v>
+        <v>0.0593</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1581</v>
+        <v>-2.0763</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3825</v>
+        <v>-0.478</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1954</v>
+        <v>0.1787</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1871</v>
+        <v>-0.6567</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.2291</v>
+        <v>0.2025</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2533</v>
+        <v>-0.2025</v>
       </c>
       <c r="R25" t="n">
-        <v>1.0242</v>
+        <v>0.4049</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2769</v>
+        <v>-0.1038</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0501</v>
+        <v>-0.0728</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2268</v>
+        <v>-0.0311</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.8474</v>
+        <v>-0.5951</v>
       </c>
       <c r="W25" t="n">
-        <v>-1.8474</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.5951</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>L. PAREJO CAMACHO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,145 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.2913</v>
+        <v>-5.1591</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.6296</v>
+        <v>-13.0002</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6618000000000001</v>
+        <v>7.841</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.4878</v>
+        <v>2.561100000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2534</v>
+        <v>4.549099999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.7412</v>
+        <v>-1.988000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.0317</v>
+        <v>4.903699999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0585</v>
+        <v>3.447300000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.0903</v>
+        <v>1.4565</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.4561</v>
+        <v>-2.3426</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1949</v>
+        <v>1.1019</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.651</v>
+        <v>-3.4444</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2048</v>
+        <v>-7.0858</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.2048</v>
+        <v>-19.233</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4097</v>
+        <v>12.1473</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4181</v>
+        <v>3.997300000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.393</v>
+        <v>2.3255</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0251</v>
+        <v>1.6714</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.5903</v>
+        <v>-4.6319</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>-0.9969000000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.5903</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>C.B. STARLABS MORÓN</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-5.851800000000003</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-13.8321</v>
-      </c>
-      <c r="F27" t="n">
-        <v>7.980099999999999</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2.6227</v>
-      </c>
-      <c r="H27" t="n">
-        <v>4.598199999999999</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-1.975800000000001</v>
-      </c>
-      <c r="J27" t="n">
-        <v>4.497700000000001</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.2091</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.2887</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-1.8754</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1.3893</v>
-      </c>
-      <c r="O27" t="n">
-        <v>-3.264399999999999</v>
-      </c>
-      <c r="P27" t="n">
-        <v>-7.169700000000001</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-19.4605</v>
-      </c>
-      <c r="R27" t="n">
-        <v>12.2907</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.3583</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.2223</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.1359</v>
-      </c>
-      <c r="V27" t="n">
-        <v>-4.663</v>
-      </c>
-      <c r="W27" t="n">
-        <v>-1.0914</v>
-      </c>
-      <c r="X27" t="n">
-        <v>-3.571600000000001</v>
+        <v>-3.635</v>
       </c>
     </row>
   </sheetData>
